--- a/Action-敵追加中-/Data/CSV/Platform/PlatformData.xlsx
+++ b/Action-敵追加中-/Data/CSV/Platform/PlatformData.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C124EB2-655B-48C5-A2B5-7FB697FDCE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{201030EF-7658-4DC1-BF08-586A15C465F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Stage" sheetId="1" r:id="rId1"/>
+    <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -980,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16" width="5.625" customWidth="1"/>
@@ -2940,7 +2940,7 @@
         <v>20</v>
       </c>
       <c r="L37">
-        <f t="shared" ref="L37:L43" si="13">I37*20</f>
+        <f t="shared" ref="L37:L41" si="13">I37*20</f>
         <v>100</v>
       </c>
       <c r="M37">
@@ -6179,6 +6179,112 @@
         <v>0</v>
       </c>
       <c r="P98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <v>0</v>
+      </c>
+      <c r="B99">
+        <v>-1000</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <f t="shared" ref="J99:J100" si="17">G99*20</f>
+        <v>20</v>
+      </c>
+      <c r="K99">
+        <f t="shared" ref="K99:K100" si="18">H99*20</f>
+        <v>20</v>
+      </c>
+      <c r="L99">
+        <f t="shared" ref="L99:L100" si="19">I99*20</f>
+        <v>20</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A100">
+        <v>0</v>
+      </c>
+      <c r="B100">
+        <v>-1000</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="K100">
+        <f t="shared" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="L100">
+        <f t="shared" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
         <v>0</v>
       </c>
     </row>

--- a/Action-敵追加中-/Data/CSV/Platform/PlatformData.xlsx
+++ b/Action-敵追加中-/Data/CSV/Platform/PlatformData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{201030EF-7658-4DC1-BF08-586A15C465F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E8B6EF5-7D2C-43E9-94FF-2D450822DA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3378,10 +3378,10 @@
         <v>0</v>
       </c>
       <c r="B46">
-        <v>-1000</v>
+        <v>250</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -3393,21 +3393,21 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I46">
         <v>1</v>
       </c>
       <c r="J46">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K46">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L46">
         <f t="shared" si="3"/>
@@ -3428,13 +3428,13 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="B47">
-        <v>-1000</v>
+        <v>250</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>-1050</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>1</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="J47">
         <f t="shared" si="1"/>
@@ -3460,11 +3460,11 @@
       </c>
       <c r="K47">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L47">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>2120</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -3481,13 +3481,13 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A48">
-        <v>0</v>
+        <v>-110</v>
       </c>
       <c r="B48">
-        <v>-1000</v>
+        <v>250</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>-1050</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -3502,22 +3502,22 @@
         <v>1</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="J48">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J48" si="14">G48*20</f>
         <v>20</v>
       </c>
       <c r="K48">
-        <f t="shared" si="2"/>
-        <v>20</v>
+        <f t="shared" ref="K48" si="15">H48*20</f>
+        <v>250</v>
       </c>
       <c r="L48">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <f t="shared" ref="L48" si="16">I48*20</f>
+        <v>2120</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A49">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="B49">
-        <v>-1000</v>
+        <v>250</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>-2100</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -3552,21 +3552,21 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I49">
         <v>1</v>
       </c>
       <c r="J49">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="K49">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L49">
         <f t="shared" si="3"/>
@@ -3587,13 +3587,13 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A50">
-        <v>0</v>
+        <v>-185</v>
       </c>
       <c r="B50">
-        <v>-1000</v>
+        <v>250</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>-2100</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -3605,21 +3605,21 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I50">
         <v>1</v>
       </c>
       <c r="J50">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="K50">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L50">
         <f t="shared" si="3"/>
@@ -3640,13 +3640,13 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A51">
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="B51">
-        <v>-1000</v>
+        <v>250</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>-2360</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -3661,10 +3661,10 @@
         <v>1</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J51">
         <f t="shared" si="1"/>
@@ -3672,11 +3672,11 @@
       </c>
       <c r="K51">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L51">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -3693,13 +3693,13 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A52">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="B52">
-        <v>-1000</v>
+        <v>250</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>-2360</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -3714,22 +3714,22 @@
         <v>1</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J52">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J52" si="17">G52*20</f>
         <v>20</v>
       </c>
       <c r="K52">
-        <f t="shared" si="2"/>
-        <v>20</v>
+        <f t="shared" ref="K52" si="18">H52*20</f>
+        <v>250</v>
       </c>
       <c r="L52">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <f t="shared" ref="L52" si="19">I52*20</f>
+        <v>500</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -3749,10 +3749,10 @@
         <v>0</v>
       </c>
       <c r="B53">
-        <v>-1000</v>
+        <v>250</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>-2620</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -3764,21 +3764,21 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
       <c r="J53">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="K53">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="L53">
         <f t="shared" si="3"/>
@@ -3802,10 +3802,10 @@
         <v>0</v>
       </c>
       <c r="B54">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>-2700</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3817,21 +3817,21 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I54">
         <v>1</v>
       </c>
       <c r="J54">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K54">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L54">
         <f t="shared" si="3"/>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A55">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="B55">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>-2820</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -3873,10 +3873,10 @@
         <v>1</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J55">
         <f t="shared" si="1"/>
@@ -3884,11 +3884,11 @@
       </c>
       <c r="K55">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L55">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -3905,13 +3905,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A56">
-        <v>0</v>
+        <v>-110</v>
       </c>
       <c r="B56">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>-2920</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -3926,10 +3926,10 @@
         <v>1</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J56">
         <f t="shared" si="1"/>
@@ -3937,11 +3937,11 @@
       </c>
       <c r="K56">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L56">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="M56">
         <v>0</v>
@@ -3958,13 +3958,13 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="B57">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>-3140</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -3976,21 +3976,21 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I57">
         <v>1</v>
       </c>
       <c r="J57">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>1760</v>
       </c>
       <c r="K57">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L57">
         <f t="shared" si="3"/>
@@ -4011,13 +4011,13 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="B58">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>-2920</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -4029,21 +4029,21 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I58">
         <v>1</v>
       </c>
       <c r="J58">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>1540</v>
       </c>
       <c r="K58">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L58">
         <f t="shared" si="3"/>
@@ -4064,13 +4064,13 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>0</v>
+        <v>1670</v>
       </c>
       <c r="B59">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>1</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J59">
         <f t="shared" si="1"/>
@@ -4096,11 +4096,11 @@
       </c>
       <c r="K59">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L59">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -4117,13 +4117,13 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>0</v>
+        <v>2550</v>
       </c>
       <c r="B60">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -4138,10 +4138,10 @@
         <v>1</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J60">
         <f t="shared" si="1"/>
@@ -4149,11 +4149,11 @@
       </c>
       <c r="K60">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L60">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -4170,13 +4170,13 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>0</v>
+        <v>2770</v>
       </c>
       <c r="B61">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>-2920</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -4188,21 +4188,21 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I61">
         <v>1</v>
       </c>
       <c r="J61">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="K61">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L61">
         <f t="shared" si="3"/>
@@ -4223,13 +4223,13 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A62">
-        <v>0</v>
+        <v>2770</v>
       </c>
       <c r="B62">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>-3140</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -4241,21 +4241,21 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I62">
         <v>1</v>
       </c>
       <c r="J62">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="K62">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L62">
         <f t="shared" si="3"/>
@@ -4276,13 +4276,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>0</v>
+        <v>2970</v>
       </c>
       <c r="B63">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>-2720</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -4297,10 +4297,10 @@
         <v>1</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J63">
         <f t="shared" si="1"/>
@@ -4308,11 +4308,11 @@
       </c>
       <c r="K63">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="L63">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -4329,13 +4329,13 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>0</v>
+        <v>2970</v>
       </c>
       <c r="B64">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>-3340</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -4350,22 +4350,22 @@
         <v>1</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I64">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J64">
-        <f t="shared" ref="J64:J98" si="14">G64*20</f>
+        <f t="shared" ref="J64:J98" si="20">G64*20</f>
         <v>20</v>
       </c>
       <c r="K64">
-        <f t="shared" ref="K64:K98" si="15">H64*20</f>
-        <v>20</v>
+        <f t="shared" ref="K64:K98" si="21">H64*20</f>
+        <v>250</v>
       </c>
       <c r="L64">
-        <f t="shared" ref="L64:L98" si="16">I64*20</f>
-        <v>20</v>
+        <f t="shared" ref="L64:L98" si="22">I64*20</f>
+        <v>380</v>
       </c>
       <c r="M64">
         <v>0</v>
@@ -4382,13 +4382,13 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="B65">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>-2520</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -4400,24 +4400,24 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I65">
         <v>1</v>
       </c>
       <c r="J65">
-        <f t="shared" si="14"/>
-        <v>20</v>
+        <f t="shared" si="20"/>
+        <v>1000</v>
       </c>
       <c r="K65">
-        <f t="shared" si="15"/>
-        <v>20</v>
+        <f t="shared" si="21"/>
+        <v>250</v>
       </c>
       <c r="L65">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M65">
@@ -4435,13 +4435,13 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="B66">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>-3540</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -4453,24 +4453,24 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I66">
         <v>1</v>
       </c>
       <c r="J66">
-        <f t="shared" si="14"/>
-        <v>20</v>
+        <f t="shared" si="20"/>
+        <v>1000</v>
       </c>
       <c r="K66">
-        <f t="shared" si="15"/>
-        <v>20</v>
+        <f t="shared" si="21"/>
+        <v>250</v>
       </c>
       <c r="L66">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M66">
@@ -4488,13 +4488,13 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>0</v>
+        <v>3990</v>
       </c>
       <c r="B67">
-        <v>-1000</v>
+        <v>450</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -4509,22 +4509,22 @@
         <v>1</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J67">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K67">
-        <f t="shared" si="15"/>
-        <v>20</v>
+        <f t="shared" si="21"/>
+        <v>250</v>
       </c>
       <c r="L67">
-        <f t="shared" si="16"/>
-        <v>20</v>
+        <f t="shared" si="22"/>
+        <v>1000</v>
       </c>
       <c r="M67">
         <v>0</v>
@@ -4568,15 +4568,15 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K68">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L68">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M68">
@@ -4621,15 +4621,15 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K69">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L69">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M69">
@@ -4674,15 +4674,15 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L70">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M70">
@@ -4727,15 +4727,15 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K71">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L71">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M71">
@@ -4780,15 +4780,15 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K72">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L72">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M72">
@@ -4833,15 +4833,15 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K73">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L73">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M73">
@@ -4886,15 +4886,15 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K74">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L74">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M74">
@@ -4939,15 +4939,15 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K75">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M75">
@@ -4992,15 +4992,15 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K76">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M76">
@@ -5045,15 +5045,15 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K77">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M77">
@@ -5098,15 +5098,15 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K78">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M78">
@@ -5151,15 +5151,15 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K79">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M79">
@@ -5204,15 +5204,15 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K80">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M80">
@@ -5257,15 +5257,15 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K81">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L81">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M81">
@@ -5310,15 +5310,15 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K82">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L82">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M82">
@@ -5363,15 +5363,15 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L83">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M83">
@@ -5416,15 +5416,15 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K84">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L84">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M84">
@@ -5469,15 +5469,15 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K85">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L85">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M85">
@@ -5522,15 +5522,15 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K86">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L86">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M86">
@@ -5575,15 +5575,15 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K87">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L87">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M87">
@@ -5628,15 +5628,15 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M88">
@@ -5681,15 +5681,15 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K89">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M89">
@@ -5734,15 +5734,15 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M90">
@@ -5787,15 +5787,15 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K91">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M91">
@@ -5840,15 +5840,15 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K92">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M92">
@@ -5893,15 +5893,15 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K93">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L93">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M93">
@@ -5946,15 +5946,15 @@
         <v>1</v>
       </c>
       <c r="J94">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K94">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L94">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M94">
@@ -5999,15 +5999,15 @@
         <v>1</v>
       </c>
       <c r="J95">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M95">
@@ -6052,15 +6052,15 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M96">
@@ -6105,15 +6105,15 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K97">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M97">
@@ -6158,15 +6158,15 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M98">
@@ -6211,15 +6211,15 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <f t="shared" ref="J99:J100" si="17">G99*20</f>
+        <f t="shared" ref="J99:J100" si="23">G99*20</f>
         <v>20</v>
       </c>
       <c r="K99">
-        <f t="shared" ref="K99:K100" si="18">H99*20</f>
+        <f t="shared" ref="K99:K100" si="24">H99*20</f>
         <v>20</v>
       </c>
       <c r="L99">
-        <f t="shared" ref="L99:L100" si="19">I99*20</f>
+        <f t="shared" ref="L99:L100" si="25">I99*20</f>
         <v>20</v>
       </c>
       <c r="M99">
@@ -6264,15 +6264,15 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K100">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L100">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M100">
